--- a/data/attendance/AMPHI_رامي_رياضيات.xlsx
+++ b/data/attendance/AMPHI_رامي_رياضيات.xlsx
@@ -304,7 +304,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
   <si>
-    <t>رامي رياضيات  |  AMPHI  |  BAC  |  رامي بن سعيد</t>
+    <t>رامي رياضيات  |  AMPHI  |  BAC  |  بن سعيد رامي</t>
   </si>
   <si>
     <t>class_id=98</t>

--- a/data/attendance/AMPHI_رامي_رياضيات.xlsx
+++ b/data/attendance/AMPHI_رامي_رياضيات.xlsx
@@ -20,280 +20,266 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <t>student_id:93669b58-0e24-4d8f-bf72-a36639e4c200</t>
+          <t>student_id:c417fe7c-ba6e-4195-a1ed-520e1b452ce5</t>
         </r>
       </text>
     </comment>
     <comment ref="B6" authorId="0">
       <text>
         <r>
-          <t>student_id:90ffae96-645a-471c-9f9d-ec9fb4a450b2</t>
+          <t>student_id:dc11c276-87ce-4add-837c-ebf1e1a0382b</t>
         </r>
       </text>
     </comment>
     <comment ref="B7" authorId="0">
       <text>
         <r>
-          <t>student_id:dc184aeb-c151-4cc4-bbac-41d08f07e8bc</t>
+          <t>student_id:7c304947-c1b3-4c67-8e59-f37da13ee991</t>
         </r>
       </text>
     </comment>
     <comment ref="B8" authorId="0">
       <text>
         <r>
-          <t>student_id:9df37305-bf32-4fd9-b352-fd3b5efdb646</t>
+          <t>student_id:73c36471-52ee-4296-9a4a-4a189451ae78</t>
         </r>
       </text>
     </comment>
     <comment ref="B9" authorId="0">
       <text>
         <r>
-          <t>student_id:5114cbcd-7528-48ac-a694-c5087cb73f85</t>
+          <t>student_id:456f9d59-492e-4d97-b626-6413bd8d358a</t>
         </r>
       </text>
     </comment>
     <comment ref="B10" authorId="0">
       <text>
         <r>
-          <t>student_id:659a26ee-c750-40b3-8e55-b2f9d2be182b</t>
+          <t>student_id:89755b77-5f80-4d26-af99-ccf407d05e5f</t>
         </r>
       </text>
     </comment>
     <comment ref="B11" authorId="0">
       <text>
         <r>
-          <t>student_id:53e9ed69-38ba-4d5b-9eac-84eb15c5796b</t>
+          <t>student_id:60414d6c-511f-4470-9144-3c0eab688966</t>
         </r>
       </text>
     </comment>
     <comment ref="B12" authorId="0">
       <text>
         <r>
-          <t>student_id:ea5fb500-ddd8-47aa-90d6-97d9cef8de8d</t>
+          <t>student_id:3e59e8b7-8a41-4fcf-a7f5-5c9d2b01b380</t>
         </r>
       </text>
     </comment>
     <comment ref="B13" authorId="0">
       <text>
         <r>
-          <t>student_id:bd2e445c-ca0a-4410-82cb-d35dc69071c0</t>
+          <t>student_id:63540332-9490-4dc7-ba5d-f4bd6638f9b0</t>
         </r>
       </text>
     </comment>
     <comment ref="B14" authorId="0">
       <text>
         <r>
-          <t>student_id:2da8f196-bda8-4b2d-8a10-ff9565c9a131</t>
+          <t>student_id:a9f2b729-1881-4aa9-8b7f-c010c77d6ff9</t>
         </r>
       </text>
     </comment>
     <comment ref="B15" authorId="0">
       <text>
         <r>
-          <t>student_id:4e475b9b-41cf-4e28-9c45-df73dfb4933b</t>
+          <t>student_id:4578980d-ce40-4241-a7f9-008902aa677c</t>
         </r>
       </text>
     </comment>
     <comment ref="B16" authorId="0">
       <text>
         <r>
-          <t>student_id:a0cadd40-08d9-4405-883e-ac2976ab5688</t>
+          <t>student_id:d5fb65ec-ce20-4077-aa63-763578087dd3</t>
         </r>
       </text>
     </comment>
     <comment ref="B17" authorId="0">
       <text>
         <r>
-          <t>student_id:7fa05c28-f61b-4881-828d-460d372ddd5b</t>
+          <t>student_id:486de26d-2d1f-4afe-9e7e-e4d3f8521232</t>
         </r>
       </text>
     </comment>
     <comment ref="B18" authorId="0">
       <text>
         <r>
-          <t>student_id:bfb57f91-b1a1-47ac-b56d-8d21f524cbb0</t>
+          <t>student_id:14cb0724-6979-4336-a565-3fcdcbc131c9</t>
         </r>
       </text>
     </comment>
     <comment ref="B19" authorId="0">
       <text>
         <r>
-          <t>student_id:a480cf1b-8ad1-4f73-a638-bc2411357a0b</t>
+          <t>student_id:3e91853b-5669-4fca-a4a4-5748c463c2b4</t>
         </r>
       </text>
     </comment>
     <comment ref="B20" authorId="0">
       <text>
         <r>
-          <t>student_id:7d24c88d-a903-4fda-b582-9433eb81f7c1</t>
+          <t>student_id:b5ade5f3-b54f-4859-9187-61a5e180e1b0</t>
         </r>
       </text>
     </comment>
     <comment ref="B21" authorId="0">
       <text>
         <r>
-          <t>student_id:c15c2d4f-5b5f-459c-a59a-185bece454be</t>
+          <t>student_id:cf423c40-e6cf-4565-9a1c-2dc7a984baf3</t>
         </r>
       </text>
     </comment>
     <comment ref="B22" authorId="0">
       <text>
         <r>
-          <t>student_id:10fb66af-e12a-4e8d-ab67-e5a259af467c</t>
+          <t>student_id:f6d7b342-ed3c-4cba-b3f0-9277bbeec11f</t>
         </r>
       </text>
     </comment>
     <comment ref="B23" authorId="0">
       <text>
         <r>
-          <t>student_id:06249712-b4ad-4c65-a9dd-4c968b79948b</t>
+          <t>student_id:6c100576-061b-499f-ba1a-d7bb8f55165d</t>
         </r>
       </text>
     </comment>
     <comment ref="B24" authorId="0">
       <text>
         <r>
-          <t>student_id:376eb7d6-44b5-4f35-95e6-3b99d7ced704</t>
+          <t>student_id:7361be5d-4675-443b-8153-6b09633fa53d</t>
         </r>
       </text>
     </comment>
     <comment ref="B25" authorId="0">
       <text>
         <r>
-          <t>student_id:5463b1a2-0dfc-48ea-94c8-90c840bd897a</t>
+          <t>student_id:99c0f747-5d9f-4906-8e9c-2577a922ce43</t>
         </r>
       </text>
     </comment>
     <comment ref="B26" authorId="0">
       <text>
         <r>
-          <t>student_id:7eaff2d6-fdf7-4805-a661-6c752063395d</t>
+          <t>student_id:e394f828-4d5f-4fd4-a81c-4c59bac598b3</t>
         </r>
       </text>
     </comment>
     <comment ref="B27" authorId="0">
       <text>
         <r>
-          <t>student_id:947d0e34-94f0-4b57-97c8-a5d69ab9484f</t>
+          <t>student_id:79cf8c30-282a-4e2a-8c6c-6b1c0747828a</t>
         </r>
       </text>
     </comment>
     <comment ref="B28" authorId="0">
       <text>
         <r>
-          <t>student_id:be563be4-7907-4a2c-b8ff-1c493af9f882</t>
+          <t>student_id:03656239-5cb8-4553-9997-ebc6b4b96823</t>
         </r>
       </text>
     </comment>
     <comment ref="B29" authorId="0">
       <text>
         <r>
-          <t>student_id:31077d84-9d42-4afd-b686-a9cc9b0f4ac3</t>
+          <t>student_id:72d56312-30fe-46f5-98f7-cf9ba5c893b0</t>
         </r>
       </text>
     </comment>
     <comment ref="B30" authorId="0">
       <text>
         <r>
-          <t>student_id:4df42bad-7508-4b32-8fd2-d8153c43bca4</t>
+          <t>student_id:5c2f6fa0-3ba1-4862-8b92-ee7bac5ca538</t>
         </r>
       </text>
     </comment>
     <comment ref="B31" authorId="0">
       <text>
         <r>
-          <t>student_id:9734566c-a3ff-430a-a2e9-7bcd3479eeed</t>
+          <t>student_id:3f1ed6fc-cf7d-41db-af33-af7e7d2ea58e</t>
         </r>
       </text>
     </comment>
     <comment ref="B32" authorId="0">
       <text>
         <r>
-          <t>student_id:8cd69b29-a816-44ee-a434-04d9e08071d7</t>
+          <t>student_id:b2e3a165-c4ae-4902-891c-ee68775c5682</t>
         </r>
       </text>
     </comment>
     <comment ref="B33" authorId="0">
       <text>
         <r>
-          <t>student_id:739e6c85-7c54-4d87-9d20-69617c3e2dda</t>
+          <t>student_id:de615a20-083f-47d6-ad76-a13a99b4b6c7</t>
         </r>
       </text>
     </comment>
     <comment ref="B34" authorId="0">
       <text>
         <r>
-          <t>student_id:afdc700f-9176-487f-b454-c48122f4a98f</t>
+          <t>student_id:23f519e2-bcf9-4c56-94d1-1638577cb3c1</t>
         </r>
       </text>
     </comment>
     <comment ref="B35" authorId="0">
       <text>
         <r>
-          <t>student_id:e285f319-bc06-4192-92a0-8ffddb131dd3</t>
+          <t>student_id:d95836b0-65db-4b54-b608-c42704af3b92</t>
         </r>
       </text>
     </comment>
     <comment ref="B36" authorId="0">
       <text>
         <r>
-          <t>student_id:5fabd3fc-e170-421e-9c44-cbf149c31a64</t>
+          <t>student_id:0bd56050-ea45-4346-8f3b-cc9827e82cca</t>
         </r>
       </text>
     </comment>
     <comment ref="B37" authorId="0">
       <text>
         <r>
-          <t>student_id:f111a9e2-c988-40e3-aaf4-2537e5167433</t>
+          <t>student_id:96da617b-eb52-4758-a89e-bdafd82a722d</t>
         </r>
       </text>
     </comment>
     <comment ref="B38" authorId="0">
       <text>
         <r>
-          <t>student_id:fa9b29e8-3df8-44d2-8b26-73c6301ac4d4</t>
+          <t>student_id:6c02f4e7-44b8-4832-a6dc-ed0504bc5b53</t>
         </r>
       </text>
     </comment>
     <comment ref="B39" authorId="0">
       <text>
         <r>
-          <t>student_id:2fbc8bc6-e3a5-44f2-89a2-71bfce734ef8</t>
+          <t>student_id:a35af6d7-6f17-4a6f-94e0-58b818839730</t>
         </r>
       </text>
     </comment>
     <comment ref="B40" authorId="0">
       <text>
         <r>
-          <t>student_id:df4a965e-1dfb-453b-88eb-9260ace95920</t>
+          <t>student_id:da0cc2e0-7750-4cec-a9c4-c5cab3fe1654</t>
         </r>
       </text>
     </comment>
     <comment ref="B41" authorId="0">
       <text>
         <r>
-          <t>student_id:fe0f417c-ff2b-420f-8da1-5eb9ed28035e</t>
+          <t>student_id:cc4cea7a-0c95-42ef-ac69-aa956f834215</t>
         </r>
       </text>
     </comment>
     <comment ref="B42" authorId="0">
       <text>
         <r>
-          <t>student_id:7afb7d37-f6e2-402a-845c-f851358a2a0d</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B43" authorId="0">
-      <text>
-        <r>
-          <t>student_id:35883d42-4c0a-47e4-ab09-fffac0d2c6e0</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B44" authorId="0">
-      <text>
-        <r>
-          <t>student_id:45fbd681-4ffd-4c38-ae98-00de0f7fad52</t>
+          <t>student_id:1dcb62ad-1b73-4e76-aea7-27cbb1e00069</t>
         </r>
       </text>
     </comment>
@@ -302,7 +288,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="57">
   <si>
     <t>رامي رياضيات  |  AMPHI  |  BAC  |  بن سعيد رامي</t>
   </si>
@@ -328,57 +314,63 @@
     <t/>
   </si>
   <si>
-    <t>بلخميس محمد منجد</t>
+    <t>جلواط أنس</t>
+  </si>
+  <si>
+    <t>بوكعباش ملاك</t>
+  </si>
+  <si>
+    <t>كحول رميساء</t>
+  </si>
+  <si>
+    <t>مرمول حسنى</t>
+  </si>
+  <si>
+    <t>شروانة ميسان</t>
+  </si>
+  <si>
+    <t>بن دكوم أشرف</t>
   </si>
   <si>
     <t>بروة يحي جاد</t>
   </si>
   <si>
+    <t>حمادو هديل</t>
+  </si>
+  <si>
+    <t>العايب رنيم</t>
+  </si>
+  <si>
+    <t>شبايكي شهد</t>
+  </si>
+  <si>
+    <t>داودي سندس</t>
+  </si>
+  <si>
+    <t>حبشي نهاد</t>
+  </si>
+  <si>
+    <t>عياد وئام</t>
+  </si>
+  <si>
+    <t>مهناوي ايناس</t>
+  </si>
+  <si>
+    <t>جلوط نسرين</t>
+  </si>
+  <si>
+    <t>نايت حمود أنفال</t>
+  </si>
+  <si>
+    <t>غبيش عبد المغيث</t>
+  </si>
+  <si>
+    <t>الفوال عبد الرحمان</t>
+  </si>
+  <si>
     <t>عويدي سرين هديل</t>
   </si>
   <si>
-    <t>بن دكوم أشرف</t>
-  </si>
-  <si>
-    <t>حمادو هديل</t>
-  </si>
-  <si>
-    <t>شبايكي شهد</t>
-  </si>
-  <si>
-    <t>داودي سندس</t>
-  </si>
-  <si>
-    <t>حبشي نهاد</t>
-  </si>
-  <si>
-    <t>عياد وئام</t>
-  </si>
-  <si>
-    <t>جلواط أنس</t>
-  </si>
-  <si>
-    <t>بوكعباش ملاك</t>
-  </si>
-  <si>
-    <t>كحول رميساء</t>
-  </si>
-  <si>
-    <t>مهناوي ايناس</t>
-  </si>
-  <si>
-    <t>جلوط نسرين</t>
-  </si>
-  <si>
-    <t>نايت حمود أنفال</t>
-  </si>
-  <si>
-    <t>غبيش عبد المغيث</t>
-  </si>
-  <si>
-    <t>الفوال عبد الرحمان</t>
-  </si>
-  <si>
     <t>عصام مرام شروق</t>
   </si>
   <si>
@@ -388,7 +380,7 @@
     <t>مباركي بشرى</t>
   </si>
   <si>
-    <t>واعمرني أماني</t>
+    <t>واعمر مي أماني</t>
   </si>
   <si>
     <t>شعبي سرين</t>
@@ -403,9 +395,6 @@
     <t>بن صالحية مرام</t>
   </si>
   <si>
-    <t>شروانة ميسان</t>
-  </si>
-  <si>
     <t>عقابي اسراء</t>
   </si>
   <si>
@@ -433,19 +422,10 @@
     <t>منصوري اسمهان</t>
   </si>
   <si>
-    <t>مرمول حسنى</t>
-  </si>
-  <si>
     <t>جيطني عبيد سماح</t>
   </si>
   <si>
-    <t>العايب رنيم</t>
-  </si>
-  <si>
     <t>مراحي لينا</t>
-  </si>
-  <si>
-    <t>باسوط ملاك</t>
   </si>
   <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
@@ -965,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1090,7 +1070,7 @@
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>190</v>
+        <v>19</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>8</v>
@@ -1134,7 +1114,7 @@
     </row>
     <row r="6" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>264</v>
+        <v>29</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>9</v>
@@ -1178,7 +1158,7 @@
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>293</v>
+        <v>32</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>10</v>
@@ -1222,7 +1202,7 @@
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>346</v>
+        <v>53</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>11</v>
@@ -1266,7 +1246,7 @@
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>376</v>
+        <v>63</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>12</v>
@@ -1310,7 +1290,7 @@
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>400</v>
+        <v>77</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>13</v>
@@ -1354,7 +1334,7 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>410</v>
+        <v>80</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>14</v>
@@ -1398,7 +1378,7 @@
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>413</v>
+        <v>106</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>15</v>
@@ -1442,7 +1422,7 @@
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>414</v>
+        <v>110</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>16</v>
@@ -1486,7 +1466,7 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>415</v>
+        <v>161</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>17</v>
@@ -1530,7 +1510,7 @@
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>416</v>
+        <v>183</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>18</v>
@@ -1574,7 +1554,7 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>417</v>
+        <v>190</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>19</v>
@@ -1618,7 +1598,7 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>418</v>
+        <v>191</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>20</v>
@@ -1662,7 +1642,7 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>419</v>
+        <v>192</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>21</v>
@@ -1706,7 +1686,7 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>420</v>
+        <v>193</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>22</v>
@@ -1750,7 +1730,7 @@
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>421</v>
+        <v>194</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>23</v>
@@ -1794,7 +1774,7 @@
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>422</v>
+        <v>195</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>24</v>
@@ -1838,7 +1818,7 @@
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>423</v>
+        <v>196</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>25</v>
@@ -1882,7 +1862,7 @@
     </row>
     <row r="23" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>424</v>
+        <v>197</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>26</v>
@@ -1926,7 +1906,7 @@
     </row>
     <row r="24" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>425</v>
+        <v>198</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>27</v>
@@ -1970,7 +1950,7 @@
     </row>
     <row r="25" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>426</v>
+        <v>199</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>28</v>
@@ -2014,7 +1994,7 @@
     </row>
     <row r="26" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>427</v>
+        <v>200</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>29</v>
@@ -2058,7 +2038,7 @@
     </row>
     <row r="27" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>428</v>
+        <v>201</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>30</v>
@@ -2102,7 +2082,7 @@
     </row>
     <row r="28" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>429</v>
+        <v>202</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>31</v>
@@ -2146,7 +2126,7 @@
     </row>
     <row r="29" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>430</v>
+        <v>203</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>32</v>
@@ -2190,7 +2170,7 @@
     </row>
     <row r="30" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>431</v>
+        <v>204</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>33</v>
@@ -2234,7 +2214,7 @@
     </row>
     <row r="31" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>432</v>
+        <v>205</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>34</v>
@@ -2278,7 +2258,7 @@
     </row>
     <row r="32" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>433</v>
+        <v>206</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>35</v>
@@ -2322,7 +2302,7 @@
     </row>
     <row r="33" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>434</v>
+        <v>207</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>36</v>
@@ -2366,7 +2346,7 @@
     </row>
     <row r="34" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>435</v>
+        <v>208</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>37</v>
@@ -2410,7 +2390,7 @@
     </row>
     <row r="35" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>436</v>
+        <v>209</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>38</v>
@@ -2454,7 +2434,7 @@
     </row>
     <row r="36" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>437</v>
+        <v>210</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>39</v>
@@ -2498,7 +2478,7 @@
     </row>
     <row r="37" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>438</v>
+        <v>211</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>40</v>
@@ -2542,7 +2522,7 @@
     </row>
     <row r="38" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>439</v>
+        <v>212</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>41</v>
@@ -2586,7 +2566,7 @@
     </row>
     <row r="39" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>440</v>
+        <v>213</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>42</v>
@@ -2630,7 +2610,7 @@
     </row>
     <row r="40" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>441</v>
+        <v>214</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>43</v>
@@ -2674,7 +2654,7 @@
     </row>
     <row r="41" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>442</v>
+        <v>215</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>44</v>
@@ -2718,7 +2698,7 @@
     </row>
     <row r="42" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>443</v>
+        <v>216</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>45</v>
@@ -2757,94 +2737,6 @@
         <v>0</v>
       </c>
       <c r="N42" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
-        <v>444</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" s="8">
-        <v>0</v>
-      </c>
-      <c r="D43" s="8">
-        <v>0</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0</v>
-      </c>
-      <c r="F43" s="8">
-        <v>0</v>
-      </c>
-      <c r="G43" s="8">
-        <v>0</v>
-      </c>
-      <c r="H43" s="8">
-        <v>0</v>
-      </c>
-      <c r="I43" s="8">
-        <v>0</v>
-      </c>
-      <c r="J43" s="8">
-        <v>0</v>
-      </c>
-      <c r="K43" s="8">
-        <v>0</v>
-      </c>
-      <c r="L43" s="8">
-        <v>0</v>
-      </c>
-      <c r="M43" s="8">
-        <v>0</v>
-      </c>
-      <c r="N43" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
-        <v>445</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C44" s="9">
-        <v>0</v>
-      </c>
-      <c r="D44" s="9">
-        <v>0</v>
-      </c>
-      <c r="E44" s="9">
-        <v>0</v>
-      </c>
-      <c r="F44" s="9">
-        <v>0</v>
-      </c>
-      <c r="G44" s="9">
-        <v>0</v>
-      </c>
-      <c r="H44" s="9">
-        <v>0</v>
-      </c>
-      <c r="I44" s="9">
-        <v>0</v>
-      </c>
-      <c r="J44" s="9">
-        <v>0</v>
-      </c>
-      <c r="K44" s="9">
-        <v>0</v>
-      </c>
-      <c r="L44" s="9">
-        <v>0</v>
-      </c>
-      <c r="M44" s="9">
-        <v>0</v>
-      </c>
-      <c r="N44" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2872,7 +2764,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -2882,12 +2774,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -2897,27 +2789,27 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -2927,12 +2819,12 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -2942,7 +2834,7 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/data/attendance/AMPHI_رامي_رياضيات.xlsx
+++ b/data/attendance/AMPHI_رامي_رياضيات.xlsx
@@ -288,7 +288,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
   <si>
     <t>رامي رياضيات  |  AMPHI  |  BAC  |  بن سعيد رامي</t>
   </si>
@@ -302,6 +302,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -368,7 +371,7 @@
     <t>الفوال عبد الرحمان</t>
   </si>
   <si>
-    <t>عويدي سرين هديل</t>
+    <t>عويدي سيرين هديل</t>
   </si>
   <si>
     <t>عصام مرام شروق</t>
@@ -455,7 +458,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -971,7 +977,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -981,10 +987,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -1026,46 +1035,46 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -1073,7 +1082,7 @@
         <v>19</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="8">
         <v>0</v>
@@ -1117,7 +1126,7 @@
         <v>29</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="9">
         <v>0</v>
@@ -1161,7 +1170,7 @@
         <v>32</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="8">
         <v>0</v>
@@ -1205,7 +1214,7 @@
         <v>53</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="9">
         <v>0</v>
@@ -1249,7 +1258,7 @@
         <v>63</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="8">
         <v>0</v>
@@ -1293,7 +1302,7 @@
         <v>77</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="9">
         <v>0</v>
@@ -1337,7 +1346,7 @@
         <v>80</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" s="8">
         <v>0</v>
@@ -1381,7 +1390,7 @@
         <v>106</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" s="9">
         <v>0</v>
@@ -1425,7 +1434,7 @@
         <v>110</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" s="8">
         <v>0</v>
@@ -1469,7 +1478,7 @@
         <v>161</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" s="9">
         <v>0</v>
@@ -1513,7 +1522,7 @@
         <v>183</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" s="8">
         <v>0</v>
@@ -1557,7 +1566,7 @@
         <v>190</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" s="9">
         <v>0</v>
@@ -1601,7 +1610,7 @@
         <v>191</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" s="8">
         <v>0</v>
@@ -1645,7 +1654,7 @@
         <v>192</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" s="9">
         <v>0</v>
@@ -1689,7 +1698,7 @@
         <v>193</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" s="8">
         <v>0</v>
@@ -1733,7 +1742,7 @@
         <v>194</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C20" s="9">
         <v>0</v>
@@ -1777,7 +1786,7 @@
         <v>195</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C21" s="8">
         <v>0</v>
@@ -1821,7 +1830,7 @@
         <v>196</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C22" s="9">
         <v>0</v>
@@ -1865,7 +1874,7 @@
         <v>197</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" s="8">
         <v>0</v>
@@ -1909,7 +1918,7 @@
         <v>198</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C24" s="9">
         <v>0</v>
@@ -1953,7 +1962,7 @@
         <v>199</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C25" s="8">
         <v>0</v>
@@ -1997,7 +2006,7 @@
         <v>200</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C26" s="9">
         <v>0</v>
@@ -2041,7 +2050,7 @@
         <v>201</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C27" s="8">
         <v>0</v>
@@ -2085,7 +2094,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C28" s="9">
         <v>0</v>
@@ -2129,7 +2138,7 @@
         <v>203</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C29" s="8">
         <v>0</v>
@@ -2173,7 +2182,7 @@
         <v>204</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C30" s="9">
         <v>0</v>
@@ -2217,7 +2226,7 @@
         <v>205</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C31" s="8">
         <v>0</v>
@@ -2261,7 +2270,7 @@
         <v>206</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C32" s="9">
         <v>0</v>
@@ -2305,7 +2314,7 @@
         <v>207</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C33" s="8">
         <v>0</v>
@@ -2349,7 +2358,7 @@
         <v>208</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C34" s="9">
         <v>0</v>
@@ -2393,7 +2402,7 @@
         <v>209</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C35" s="8">
         <v>0</v>
@@ -2437,7 +2446,7 @@
         <v>210</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C36" s="9">
         <v>0</v>
@@ -2481,7 +2490,7 @@
         <v>211</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C37" s="8">
         <v>0</v>
@@ -2525,7 +2534,7 @@
         <v>212</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C38" s="9">
         <v>0</v>
@@ -2569,7 +2578,7 @@
         <v>213</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C39" s="8">
         <v>0</v>
@@ -2613,7 +2622,7 @@
         <v>214</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C40" s="9">
         <v>0</v>
@@ -2657,7 +2666,7 @@
         <v>215</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C41" s="8">
         <v>0</v>
@@ -2701,7 +2710,7 @@
         <v>216</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C42" s="9">
         <v>0</v>
@@ -2756,7 +2765,7 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
@@ -2764,77 +2773,82 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
